--- a/build/handover/Test-Case-Changes-for-Vlad_2026-08-12.xlsx
+++ b/build/handover/Test-Case-Changes-for-Vlad_2026-08-12.xlsx
@@ -487,6 +487,7 @@
 SECTION A IS THE ONE THAT MATTERS TO YOU. It is the 44 cases TestRail flags as Automated. For each one, the last column says whether the change alters what an automated check should conclude. 7 of the 44 do; the rest are sourcing and reference edits that change nothing you evaluate.
 ONE THING THAT APPLIES TO ALL OF SECTION A, so it is said once here rather than repeated on 44 rows: every one of them had a line added to the bottom of its expected results recording the date we read each source. If any of your checks compares the WHOLE expected-results field as one string, it will see a difference on all 44 — even the ones where nothing about the behaviour changed. If your checks read individual assertions, they will not.
 Sections B and C are for completeness. Section C is new cases, which you can see in TestRail yourself.
+READ FROM TESTRAIL AT 2026-08-12T05:53:56Z. Another worker was editing the same suites during this pass, so a handful of Schedule cases moved after this snapshot; the case ids and the Automated set are unaffected.
 Please overrule us on the last column wherever you disagree — we have never seen your scripts, and something we call cosmetic can still break a check that matches an exact string.</t>
         </is>
       </c>
@@ -6044,7 +6045,7 @@
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>SCHEDULE — 168, OF WHICH 29 HAD A REAL CHANGE</t>
+          <t>SCHEDULE — 168, OF WHICH 33 HAD A REAL CHANGE</t>
         </is>
       </c>
       <c r="B116" s="6" t="n"/>
@@ -6080,7 +6081,7 @@
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>The preconditions, steps or expected outcomes were edited. Also: Corrected on-screen names to the exact wording the build shows. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results.</t>
+          <t>The preconditions, steps or expected outcomes were edited. Also: Corrected on-screen names to the exact wording the build shows. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass.</t>
         </is>
       </c>
       <c r="G117" s="7" t="inlineStr">
@@ -6115,7 +6116,7 @@
       </c>
       <c r="F118" s="7" t="inlineStr">
         <is>
-          <t>The preconditions, steps or expected outcomes were edited. Also: Correction from the 11 August build check. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results.</t>
+          <t>The preconditions, steps or expected outcomes were edited. Also: Correction from the 11 August build check. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass.</t>
         </is>
       </c>
       <c r="G118" s="7" t="inlineStr">
@@ -6360,7 +6361,7 @@
       </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>The preconditions, steps or expected outcomes were edited. Also: The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results.</t>
+          <t>The preconditions, steps or expected outcomes were edited. Also: The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass.</t>
         </is>
       </c>
       <c r="G125" s="7" t="inlineStr">
@@ -6465,7 +6466,7 @@
       </c>
       <c r="F128" s="7" t="inlineStr">
         <is>
-          <t>The preconditions, steps or expected outcomes were edited. Also: Corrected on-screen names to the exact wording the build shows. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results.</t>
+          <t>The preconditions, steps or expected outcomes were edited. Also: Corrected on-screen names to the exact wording the build shows. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass.</t>
         </is>
       </c>
       <c r="G128" s="7" t="inlineStr">
@@ -6535,7 +6536,7 @@
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>The preconditions, steps or expected outcomes were edited. Also: Corrected on-screen names to the exact wording the build shows. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results.</t>
+          <t>The preconditions, steps or expected outcomes were edited. Also: Corrected on-screen names to the exact wording the build shows. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass.</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
@@ -6605,7 +6606,7 @@
       </c>
       <c r="F132" s="7" t="inlineStr">
         <is>
-          <t>The title changed. The preconditions, steps or expected outcomes were edited. Also: Corrected on-screen names to the exact wording the build shows. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results.</t>
+          <t>The title changed. The preconditions, steps or expected outcomes were edited. Also: Corrected on-screen names to the exact wording the build shows. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass.</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr">
@@ -6640,7 +6641,7 @@
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>The preconditions, steps or expected outcomes were edited. Also: Corrected on-screen names to the exact wording the build shows. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results.</t>
+          <t>The preconditions, steps or expected outcomes were edited. Also: Corrected on-screen names to the exact wording the build shows. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass.</t>
         </is>
       </c>
       <c r="G133" s="7" t="inlineStr">
@@ -6675,7 +6676,7 @@
       </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
-          <t>The preconditions, steps or expected outcomes were edited. Also: Corrected on-screen names to the exact wording the build shows. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results.</t>
+          <t>Automation marker moved: HOLD - needs a second sign-in as a user with no staff record of their own  -&gt;  HOLD - point 4 needs a user with no staff record of their own; points 1 to 3 are observed and pass. The preconditions, steps or expected outcomes were edited. Also: Corrected on-screen names to the exact wording the build shows. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass.</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr">
@@ -6710,7 +6711,7 @@
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>The preconditions, steps or expected outcomes were edited. Also: Corrected on-screen names to the exact wording the build shows. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results.</t>
+          <t>The preconditions, steps or expected outcomes were edited. Also: Corrected on-screen names to the exact wording the build shows. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass.</t>
         </is>
       </c>
       <c r="G135" s="7" t="inlineStr">
@@ -6745,7 +6746,7 @@
       </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
-          <t>The title changed. The preconditions, steps or expected outcomes were edited. Also: Corrected on-screen names to the exact wording the build shows. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results.</t>
+          <t>The title changed. The preconditions, steps or expected outcomes were edited. Also: Corrected on-screen names to the exact wording the build shows. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass.</t>
         </is>
       </c>
       <c r="G136" s="7" t="inlineStr">
@@ -6780,7 +6781,7 @@
       </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>The preconditions, steps or expected outcomes were edited. Also: Corrected on-screen names to the exact wording the build shows. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results.</t>
+          <t>The preconditions, steps or expected outcomes were edited. Also: Corrected on-screen names to the exact wording the build shows. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass.</t>
         </is>
       </c>
       <c r="G137" s="7" t="inlineStr">
@@ -6815,7 +6816,7 @@
       </c>
       <c r="F138" s="7" t="inlineStr">
         <is>
-          <t>The preconditions, steps or expected outcomes were edited. Also: Corrected on-screen names to the exact wording the build shows. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results.</t>
+          <t>The preconditions, steps or expected outcomes were edited. Also: Corrected on-screen names to the exact wording the build shows. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass.</t>
         </is>
       </c>
       <c r="G138" s="7" t="inlineStr">
@@ -6850,7 +6851,7 @@
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
-          <t>The title changed. The preconditions, steps or expected outcomes were edited. Also: Corrected on-screen names to the exact wording the build shows. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results.</t>
+          <t>The title changed. The preconditions, steps or expected outcomes were edited. Also: Corrected on-screen names to the exact wording the build shows. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass.</t>
         </is>
       </c>
       <c r="G139" s="7" t="inlineStr">
@@ -6865,12 +6866,12 @@
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
-          <t>C30082</t>
+          <t>C30074</t>
         </is>
       </c>
       <c r="C140" s="7" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30082</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30074</t>
         </is>
       </c>
       <c r="D140" s="7" t="inlineStr">
@@ -6880,12 +6881,12 @@
       </c>
       <c r="E140" s="7" t="inlineStr">
         <is>
-          <t>No own-only restriction: a View user sees ALL technicians' shifts</t>
+          <t>Schedule: View grants the full read-only experience across the whole page</t>
         </is>
       </c>
       <c r="F140" s="7" t="inlineStr">
         <is>
-          <t>The preconditions, steps or expected outcomes were edited. Also: Corrected on-screen names to the exact wording the build shows. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results.</t>
+          <t>Automation marker moved: HOLD - needs a second sign-in as a view-only user  -&gt;  READY. Also: The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass.</t>
         </is>
       </c>
       <c r="G140" s="7" t="inlineStr">
@@ -6900,12 +6901,12 @@
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>C38847</t>
+          <t>C30075</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/38847</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30075</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
@@ -6915,12 +6916,12 @@
       </c>
       <c r="E141" s="7" t="inlineStr">
         <is>
-          <t>Business-hours toggle reveals a per-day (Mon-Sun) From-To editor</t>
+          <t>View-only: every editing affordance is hidden or disabled</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>The preconditions, steps or expected outcomes were edited. Also: Part of the 12 August build check: the build stamp at the bottom of the case was re-cut to the build running today. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results.</t>
+          <t>Automation marker moved: HOLD - needs a second sign-in as a view-only user  -&gt;  READY. Also: The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass.</t>
         </is>
       </c>
       <c r="G141" s="7" t="inlineStr">
@@ -6935,12 +6936,12 @@
       </c>
       <c r="B142" s="7" t="inlineStr">
         <is>
-          <t>C38848</t>
+          <t>C30082</t>
         </is>
       </c>
       <c r="C142" s="7" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/38848</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30082</t>
         </is>
       </c>
       <c r="D142" s="7" t="inlineStr">
@@ -6950,12 +6951,12 @@
       </c>
       <c r="E142" s="7" t="inlineStr">
         <is>
-          <t>Edit Staff has a 'Set working hours for this technician' toggle, off by default</t>
+          <t>No own-only restriction: a View user sees ALL technicians' shifts</t>
         </is>
       </c>
       <c r="F142" s="7" t="inlineStr">
         <is>
-          <t>The title changed. The preconditions, steps or expected outcomes were edited. Also: Part of the 12 August build check: the build stamp at the bottom of the case was re-cut to the build running today. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results.</t>
+          <t>Automation marker moved: HOLD - needs a second sign-in as a view-only technician  -&gt;  READY. The preconditions, steps or expected outcomes were edited. Also: Corrected on-screen names to the exact wording the build shows. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass.</t>
         </is>
       </c>
       <c r="G142" s="7" t="inlineStr">
@@ -6970,12 +6971,12 @@
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
-          <t>C38849</t>
+          <t>C38847</t>
         </is>
       </c>
       <c r="C143" s="7" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/38849</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/38847</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
@@ -6985,7 +6986,7 @@
       </c>
       <c r="E143" s="7" t="inlineStr">
         <is>
-          <t>A technician with no custom hours inherits the shop business hours</t>
+          <t>Business-hours toggle reveals a per-day (Mon-Sun) From-To editor</t>
         </is>
       </c>
       <c r="F143" s="7" t="inlineStr">
@@ -7005,12 +7006,12 @@
       </c>
       <c r="B144" s="7" t="inlineStr">
         <is>
-          <t>C38850</t>
+          <t>C38848</t>
         </is>
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/38850</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/38848</t>
         </is>
       </c>
       <c r="D144" s="7" t="inlineStr">
@@ -7020,7 +7021,7 @@
       </c>
       <c r="E144" s="7" t="inlineStr">
         <is>
-          <t>'Add Hours' appends a removable second range for split shifts, starting empty</t>
+          <t>Edit Staff has a 'Set working hours for this technician' toggle, off by default</t>
         </is>
       </c>
       <c r="F144" s="7" t="inlineStr">
@@ -7040,172 +7041,172 @@
       </c>
       <c r="B145" s="7" t="inlineStr">
         <is>
+          <t>C38849</t>
+        </is>
+      </c>
+      <c r="C145" s="7" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/38849</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="inlineStr">
+        <is>
+          <t>A technician with no custom hours inherits the shop business hours</t>
+        </is>
+      </c>
+      <c r="F145" s="7" t="inlineStr">
+        <is>
+          <t>The preconditions, steps or expected outcomes were edited. Also: Part of the 12 August build check: the build stamp at the bottom of the case was re-cut to the build running today. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results.</t>
+        </is>
+      </c>
+      <c r="G145" s="7" t="inlineStr">
+        <is>
+          <t>YES — something a check reads changed. Please look at this one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="80" customHeight="1">
+      <c r="A146" s="7" t="n">
+        <v>140</v>
+      </c>
+      <c r="B146" s="7" t="inlineStr">
+        <is>
+          <t>C38850</t>
+        </is>
+      </c>
+      <c r="C146" s="7" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/38850</t>
+        </is>
+      </c>
+      <c r="D146" s="7" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E146" s="7" t="inlineStr">
+        <is>
+          <t>'Add Hours' appends a removable second range for split shifts, starting empty</t>
+        </is>
+      </c>
+      <c r="F146" s="7" t="inlineStr">
+        <is>
+          <t>The title changed. The preconditions, steps or expected outcomes were edited. Also: Part of the 12 August build check: the build stamp at the bottom of the case was re-cut to the build running today. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results.</t>
+        </is>
+      </c>
+      <c r="G146" s="7" t="inlineStr">
+        <is>
+          <t>YES — something a check reads changed. Please look at this one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="80" customHeight="1">
+      <c r="A147" s="7" t="n">
+        <v>141</v>
+      </c>
+      <c r="B147" s="7" t="inlineStr">
+        <is>
+          <t>C38872</t>
+        </is>
+      </c>
+      <c r="C147" s="7" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/38872</t>
+        </is>
+      </c>
+      <c r="D147" s="7" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E147" s="7" t="inlineStr">
+        <is>
+          <t>API - Schedule reads need View; writes need Edit; deletes need Delete (403)</t>
+        </is>
+      </c>
+      <c r="F147" s="7" t="inlineStr">
+        <is>
+          <t>Automation marker moved: HOLD - needs three separate sign-ins, one per permission level  -&gt;  HOLD - points 1 and 3 need a user with no Schedule permission and a user with Schedule Edit but not Delete; point 2 is observed and passes. Also: The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass.</t>
+        </is>
+      </c>
+      <c r="G147" s="7" t="inlineStr">
+        <is>
+          <t>YES — something a check reads changed. Please look at this one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="80" customHeight="1">
+      <c r="A148" s="7" t="n">
+        <v>142</v>
+      </c>
+      <c r="B148" s="7" t="inlineStr">
+        <is>
+          <t>C38874</t>
+        </is>
+      </c>
+      <c r="C148" s="7" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/38874</t>
+        </is>
+      </c>
+      <c r="D148" s="7" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t>API - No pricing fields in Schedule responses; WO details need Work Orders View</t>
+        </is>
+      </c>
+      <c r="F148" s="7" t="inlineStr">
+        <is>
+          <t>Automation marker moved: HOLD - needs a second sign-in as a user who cannot see work orders  -&gt;  HOLD - point 2 needs a user without Work Orders View; point 1 is observed and passes. Also: The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass.</t>
+        </is>
+      </c>
+      <c r="G148" s="7" t="inlineStr">
+        <is>
+          <t>YES — something a check reads changed. Please look at this one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="80" customHeight="1">
+      <c r="A149" s="7" t="n">
+        <v>143</v>
+      </c>
+      <c r="B149" s="7" t="inlineStr">
+        <is>
           <t>C38926</t>
         </is>
       </c>
-      <c r="C145" s="7" t="inlineStr">
+      <c r="C149" s="7" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/38926</t>
         </is>
       </c>
-      <c r="D145" s="7" t="inlineStr">
+      <c r="D149" s="7" t="inlineStr">
         <is>
           <t>Schedule</t>
         </is>
       </c>
-      <c r="E145" s="7" t="inlineStr">
+      <c r="E149" s="7" t="inlineStr">
         <is>
           <t>Default roles start at the Schedule level the spec names (view-only vs edit)</t>
         </is>
       </c>
-      <c r="F145" s="7" t="inlineStr">
+      <c r="F149" s="7" t="inlineStr">
         <is>
           <t>The preconditions, steps or expected outcomes were edited. Also: Part of the 12 August build check: the build stamp at the bottom of the case was re-cut to the build running today. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results.</t>
         </is>
       </c>
-      <c r="G145" s="7" t="inlineStr">
+      <c r="G149" s="7" t="inlineStr">
         <is>
           <t>YES — something a check reads changed. Please look at this one.</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="46" customHeight="1">
-      <c r="A146" s="3" t="n">
-        <v>140</v>
-      </c>
-      <c r="B146" s="3" t="inlineStr">
-        <is>
-          <t>C29925</t>
-        </is>
-      </c>
-      <c r="C146" s="3" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29925</t>
-        </is>
-      </c>
-      <c r="D146" s="3" t="inlineStr">
-        <is>
-          <t>Schedule</t>
-        </is>
-      </c>
-      <c r="E146" s="3" t="inlineStr">
-        <is>
-          <t>Schedule opens from the top-level navigation into a sidebar + grid layout</t>
-        </is>
-      </c>
-      <c r="F146" s="3" t="inlineStr">
-        <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
-        </is>
-      </c>
-      <c r="G146" s="3" t="inlineStr">
-        <is>
-          <t>No. Only the sourcing line or the References field moved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="46" customHeight="1">
-      <c r="A147" s="3" t="n">
-        <v>141</v>
-      </c>
-      <c r="B147" s="3" t="inlineStr">
-        <is>
-          <t>C29927</t>
-        </is>
-      </c>
-      <c r="C147" s="3" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29927</t>
-        </is>
-      </c>
-      <c r="D147" s="3" t="inlineStr">
-        <is>
-          <t>Schedule</t>
-        </is>
-      </c>
-      <c r="E147" s="3" t="inlineStr">
-        <is>
-          <t>Day / Week / Month segmented control switches the grid between the three views</t>
-        </is>
-      </c>
-      <c r="F147" s="3" t="inlineStr">
-        <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
-        </is>
-      </c>
-      <c r="G147" s="3" t="inlineStr">
-        <is>
-          <t>No. Only the sourcing line or the References field moved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="46" customHeight="1">
-      <c r="A148" s="3" t="n">
-        <v>142</v>
-      </c>
-      <c r="B148" s="3" t="inlineStr">
-        <is>
-          <t>C29928</t>
-        </is>
-      </c>
-      <c r="C148" s="3" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29928</t>
-        </is>
-      </c>
-      <c r="D148" s="3" t="inlineStr">
-        <is>
-          <t>Schedule</t>
-        </is>
-      </c>
-      <c r="E148" s="3" t="inlineStr">
-        <is>
-          <t>Grid rows are grouped by department under group headers</t>
-        </is>
-      </c>
-      <c r="F148" s="3" t="inlineStr">
-        <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
-        </is>
-      </c>
-      <c r="G148" s="3" t="inlineStr">
-        <is>
-          <t>No. Only the sourcing line or the References field moved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="46" customHeight="1">
-      <c r="A149" s="3" t="n">
-        <v>143</v>
-      </c>
-      <c r="B149" s="3" t="inlineStr">
-        <is>
-          <t>C29929</t>
-        </is>
-      </c>
-      <c r="C149" s="3" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29929</t>
-        </is>
-      </c>
-      <c r="D149" s="3" t="inlineStr">
-        <is>
-          <t>Schedule</t>
-        </is>
-      </c>
-      <c r="E149" s="3" t="inlineStr">
-        <is>
-          <t>Collapsing a department header hides its technician rows</t>
-        </is>
-      </c>
-      <c r="F149" s="3" t="inlineStr">
-        <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
-        </is>
-      </c>
-      <c r="G149" s="3" t="inlineStr">
-        <is>
-          <t>No. Only the sourcing line or the References field moved.</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7216,12 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>C29931</t>
+          <t>C29925</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29931</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29925</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
@@ -7230,7 +7231,7 @@
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>An Unassigned row sits inside the grid, not in a separate tray</t>
+          <t>Schedule opens from the top-level navigation into a sidebar + grid layout</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
@@ -7250,12 +7251,12 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>C29932</t>
+          <t>C29927</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29932</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29927</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
@@ -7265,7 +7266,7 @@
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>Clicking a date in the mini calendar navigates the main grid to that date</t>
+          <t>Day / Week / Month segmented control switches the grid between the three views</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
@@ -7285,12 +7286,12 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>C29933</t>
+          <t>C29928</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29933</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29928</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
@@ -7300,7 +7301,7 @@
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>Mini calendar month/year picker has month buttons and year arrows</t>
+          <t>Grid rows are grouped by department under group headers</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
@@ -7320,12 +7321,12 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>C29934</t>
+          <t>C29929</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29934</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29929</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
@@ -7335,7 +7336,7 @@
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>A chevron toggle collapses and expands the mini calendar grid</t>
+          <t>Collapsing a department header hides its technician rows</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
@@ -7355,12 +7356,12 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>C29935</t>
+          <t>C29931</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29935</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29931</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
@@ -7370,7 +7371,7 @@
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>Mini calendar highlights the selected date, today, and the hovered week</t>
+          <t>An Unassigned row sits inside the grid, not in a separate tray</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
@@ -7390,12 +7391,12 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>C29936</t>
+          <t>C29932</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29936</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29932</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
@@ -7405,7 +7406,7 @@
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>The sidebar is a flat list of work order cards with no tabs</t>
+          <t>Clicking a date in the mini calendar navigates the main grid to that date</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
@@ -7425,12 +7426,12 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>C29937</t>
+          <t>C29933</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29937</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29933</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
@@ -7440,7 +7441,7 @@
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>Work order card anatomy, incl. the status-colored left border</t>
+          <t>Mini calendar month/year picker has month buttons and year arrows</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
@@ -7460,12 +7461,12 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>C29939</t>
+          <t>C29934</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29939</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29934</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
@@ -7475,7 +7476,7 @@
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>'Search work orders' matches work order number, customer, unit, and technician</t>
+          <t>A chevron toggle collapses and expands the mini calendar grid</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
@@ -7495,12 +7496,12 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>C29940</t>
+          <t>C29935</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29940</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29935</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
@@ -7510,7 +7511,7 @@
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>Sidebar search filters the card list in real time as you type</t>
+          <t>Mini calendar highlights the selected date, today, and the hovered week</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
@@ -7530,12 +7531,12 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>C29941</t>
+          <t>C29936</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29941</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29936</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
@@ -7545,12 +7546,12 @@
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>Sidebar search with no matching work orders shows an empty list</t>
+          <t>The sidebar is a flat list of work order cards with no tabs</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
@@ -7565,12 +7566,12 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>C29942</t>
+          <t>C29937</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29942</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29937</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
@@ -7580,7 +7581,7 @@
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>The 'Filters' button opens Assignment / Status / Priority filter groups</t>
+          <t>Work order card anatomy, incl. the status-colored left border</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
@@ -7600,12 +7601,12 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>C29943</t>
+          <t>C29939</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29943</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29939</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
@@ -7615,12 +7616,12 @@
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>Assignment filter narrows the list to Assigned or Unassigned work orders</t>
+          <t>'Search work orders' matches work order number, customer, unit, and technician</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
@@ -7635,12 +7636,12 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>C29945</t>
+          <t>C29940</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29945</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29940</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
@@ -7650,12 +7651,12 @@
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>Priority filter offers High, Medium, Low and narrows the list accordingly</t>
+          <t>Sidebar search filters the card list in real time as you type</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
@@ -7670,12 +7671,12 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>C29946</t>
+          <t>C29941</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29946</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29941</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
@@ -7685,12 +7686,12 @@
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>'Clear all' resets every applied sidebar filter in one click</t>
+          <t>Sidebar search with no matching work orders shows an empty list</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
@@ -7705,12 +7706,12 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>C29947</t>
+          <t>C29942</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29947</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29942</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
@@ -7720,12 +7721,12 @@
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>Search and filter work together - both can be active at the same time</t>
+          <t>The 'Filters' button opens Assignment / Status / Priority filter groups</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
@@ -7740,12 +7741,12 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>C29948</t>
+          <t>C29943</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29948</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29943</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
@@ -7755,12 +7756,12 @@
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>Work order card opens the line drill-down in place, with header and back control</t>
+          <t>Assignment filter narrows the list to Assigned or Unassigned work orders</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
@@ -7775,12 +7776,12 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>C29950</t>
+          <t>C29945</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29950</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29945</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
@@ -7790,12 +7791,12 @@
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>Only approved work order lines appear in the drill-down</t>
+          <t>Priority filter offers High, Medium, Low and narrows the list accordingly</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
@@ -7810,12 +7811,12 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>C29951</t>
+          <t>C29946</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29951</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29946</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
@@ -7825,7 +7826,7 @@
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>Line row shows title, hours, the technician roster and a drag handle</t>
+          <t>'Clear all' resets every applied sidebar filter in one click</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
@@ -7845,12 +7846,12 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>C29952</t>
+          <t>C29947</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29952</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29947</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
@@ -7860,12 +7861,12 @@
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>Lines with no technician assigned show a 'Needs techs' badge</t>
+          <t>Search and filter work together - both can be active at the same time</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
@@ -7880,12 +7881,12 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>C29953</t>
+          <t>C29948</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29953</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29948</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
@@ -7895,7 +7896,7 @@
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>'Search lines' matches the line title/name only</t>
+          <t>Work order card opens the line drill-down in place, with header and back control</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
@@ -7915,12 +7916,12 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>C29954</t>
+          <t>C29950</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29954</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29950</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
@@ -7930,12 +7931,12 @@
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>'All / Unscheduled' filter chips show counts and filter the line list</t>
+          <t>Only approved work order lines appear in the drill-down</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
@@ -7950,12 +7951,12 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>C29955</t>
+          <t>C29951</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29955</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29951</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
@@ -7965,7 +7966,7 @@
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>Dropping a single-line work order creates a shift with no scope picker</t>
+          <t>Line row shows title, hours, the technician roster and a drag handle</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
@@ -7985,12 +7986,12 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>C29956</t>
+          <t>C29952</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29956</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29952</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
@@ -8000,7 +8001,7 @@
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>Dropping a multi-line work order on a technician cell opens the scope picker</t>
+          <t>Lines with no technician assigned show a 'Needs techs' badge</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
@@ -8020,12 +8021,12 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>C29957</t>
+          <t>C29953</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29957</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29953</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
@@ -8035,12 +8036,12 @@
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>Dragging a line from the drill-down creates a single-line shift</t>
+          <t>'Search lines' matches the line title/name only</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
@@ -8055,12 +8056,12 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>C29958</t>
+          <t>C29954</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29958</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29954</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
@@ -8070,12 +8071,12 @@
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>A job over the technician's daily hours opens the spread step</t>
+          <t>'All / Unscheduled' filter chips show counts and filter the line list</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
@@ -8090,12 +8091,12 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>C29959</t>
+          <t>C29955</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29959</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29955</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
@@ -8105,7 +8106,7 @@
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>A scope that fits one working day skips the spread step</t>
+          <t>Dropping a single-line work order creates a shift with no scope picker</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
@@ -8125,12 +8126,12 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>C29960</t>
+          <t>C29956</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29960</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29956</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
@@ -8140,12 +8141,12 @@
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>While dragging, target cells highlight and a ghost block follows</t>
+          <t>Dropping a multi-line work order on a technician cell opens the scope picker</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
@@ -8160,12 +8161,12 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>C29961</t>
+          <t>C29957</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29961</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29957</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
@@ -8175,7 +8176,7 @@
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>Scheduling a technician onto a line adds them to its labor roster</t>
+          <t>Dragging a line from the drill-down creates a single-line shift</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
@@ -8195,12 +8196,12 @@
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>C29963</t>
+          <t>C29958</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29963</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29958</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
@@ -8210,12 +8211,12 @@
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>Scope picker contents: the pinned whole-order row and the line rows</t>
+          <t>A job over the technician's daily hours opens the spread step</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
@@ -8230,12 +8231,12 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>C29964</t>
+          <t>C29959</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29964</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29959</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
@@ -8245,7 +8246,7 @@
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>'Schedule whole work order' assigns all lines and creates one shift</t>
+          <t>A scope that fits one working day skips the spread step</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
@@ -8265,12 +8266,12 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>C29965</t>
+          <t>C29960</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29965</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29960</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
@@ -8280,7 +8281,7 @@
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>Tapping a line row creates a single-line shift with no confirm step</t>
+          <t>While dragging, target cells highlight and a ghost block follows</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
@@ -8300,12 +8301,12 @@
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>C29969</t>
+          <t>C29961</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29969</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29961</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
@@ -8315,7 +8316,7 @@
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>A shift's start time uses the technician's own working hours when set</t>
+          <t>Scheduling a technician onto a line adds them to its labor roster</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
@@ -8335,12 +8336,12 @@
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>C29970</t>
+          <t>C29963</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29970</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29963</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
@@ -8350,12 +8351,12 @@
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>With no technician hours set, start time falls back to business hours</t>
+          <t>Scope picker contents: the pinned whole-order row and the line rows</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
@@ -8370,12 +8371,12 @@
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>C29971</t>
+          <t>C29964</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29971</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29964</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
@@ -8385,7 +8386,7 @@
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>With neither technician hours nor business hours set, a 7:00 AM default applies</t>
+          <t>'Schedule whole work order' assigns all lines and creates one shift</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
@@ -8405,12 +8406,12 @@
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>C29972</t>
+          <t>C29965</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29972</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29965</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
@@ -8420,12 +8421,12 @@
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>In day view the start time comes from the drop position</t>
+          <t>Tapping a line row creates a single-line shift with no confirm step</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
@@ -8440,12 +8441,12 @@
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>C29973</t>
+          <t>C29969</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29973</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29969</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
@@ -8455,7 +8456,7 @@
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>Dropping onto the Unassigned row creates a shift with no technician</t>
+          <t>A shift's start time uses the technician's own working hours when set</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
@@ -8475,12 +8476,12 @@
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>C29974</t>
+          <t>C29970</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29974</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29970</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
@@ -8490,7 +8491,7 @@
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>Unassigned shift start time uses business hours or the default</t>
+          <t>With no technician hours set, start time falls back to business hours</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
@@ -8510,12 +8511,12 @@
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>C29975</t>
+          <t>C29971</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29975</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29971</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
@@ -8525,7 +8526,7 @@
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Dragging an unassigned shift onto a technician row assigns it</t>
+          <t>With neither technician hours nor business hours set, a 7:00 AM default applies</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
@@ -8545,12 +8546,12 @@
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>C29978</t>
+          <t>C29972</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29978</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29972</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
@@ -8560,7 +8561,7 @@
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>Spread step header shows the scope; 'Change scope' returns to the picker</t>
+          <t>In day view the start time comes from the drop position</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
@@ -8580,12 +8581,12 @@
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>C29979</t>
+          <t>C29973</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29979</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29973</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
@@ -8595,7 +8596,7 @@
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>How-much selector defaults to Full estimate; preset amounts apply at once</t>
+          <t>Dropping onto the Unassigned row creates a shift with no technician</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
@@ -8615,12 +8616,12 @@
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>C29981</t>
+          <t>C29974</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29981</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29974</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
@@ -8630,7 +8631,7 @@
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>'Specific hours…' reveals an hours stepper</t>
+          <t>Unassigned shift start time uses business hours or the default</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
@@ -8650,12 +8651,12 @@
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>C29983</t>
+          <t>C29975</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29983</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29975</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
@@ -8665,7 +8666,7 @@
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>Spread uses the tech's working hours; skips weekends only when hours not set</t>
+          <t>Dragging an unassigned shift onto a technician row assigns it</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
@@ -8685,12 +8686,12 @@
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>C29986</t>
+          <t>C29978</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29986</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29978</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
@@ -8700,12 +8701,12 @@
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>The same work order on a second technician spreads the full estimate again</t>
+          <t>Spread step header shows the scope; 'Change scope' returns to the picker</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
@@ -8720,12 +8721,12 @@
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>C29987</t>
+          <t>C29979</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29987</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29979</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
@@ -8735,7 +8736,7 @@
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>Month view: series banner wraps across weeks, labeled once, then 'continues'</t>
+          <t>How-much selector defaults to Full estimate; preset amounts apply at once</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
@@ -8755,12 +8756,12 @@
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>C29988</t>
+          <t>C29981</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29988</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29981</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
@@ -8770,12 +8771,12 @@
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>Week view: series banner spans the week, with chevrons and 'week N of M'</t>
+          <t>'Specific hours…' reveals an hours stepper</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
@@ -8790,12 +8791,12 @@
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>C29989</t>
+          <t>C29983</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29989</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29983</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
@@ -8805,12 +8806,12 @@
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>Day view shows the series day as one block with a multi-week cue</t>
+          <t>Spread uses the tech's working hours; skips weekends only when hours not set</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
@@ -8825,12 +8826,12 @@
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>C29990</t>
+          <t>C29986</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29990</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29986</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
@@ -8840,12 +8841,12 @@
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>A series is just a grouping - capacity and conflicts use the daily shifts</t>
+          <t>The same work order on a second technician spreads the full estimate again</t>
         </is>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
@@ -8860,12 +8861,12 @@
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>C29991</t>
+          <t>C29987</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29991</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29987</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
@@ -8875,7 +8876,7 @@
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>A single-line shift block shows customer, unit number and line name</t>
+          <t>Month view: series banner wraps across weeks, labeled once, then 'continues'</t>
         </is>
       </c>
       <c r="F197" s="3" t="inlineStr">
@@ -8895,12 +8896,12 @@
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>C29992</t>
+          <t>C29988</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29992</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29988</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
@@ -8910,7 +8911,7 @@
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>Whole-order and multi-line shifts both read 'N Lines' on the block</t>
+          <t>Week view: series banner spans the week, with chevrons and 'week N of M'</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
@@ -8930,12 +8931,12 @@
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>C29995</t>
+          <t>C29989</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29995</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29989</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
@@ -8945,7 +8946,7 @@
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>The conflict icon is the only icon on a shift block</t>
+          <t>Day view shows the series day as one block with a multi-week cue</t>
         </is>
       </c>
       <c r="F199" s="3" t="inlineStr">
@@ -8965,12 +8966,12 @@
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>C29996</t>
+          <t>C29990</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29996</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29990</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
@@ -8980,7 +8981,7 @@
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>Non-overlapping same-day shifts share one lane, even from different orders</t>
+          <t>A series is just a grouping - capacity and conflicts use the daily shifts</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
@@ -9000,12 +9001,12 @@
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>C29997</t>
+          <t>C29991</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29997</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29991</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
@@ -9015,7 +9016,7 @@
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>Shifts whose times intersect split into stacked lanes and the row grows to fit</t>
+          <t>A single-line shift block shows customer, unit number and line name</t>
         </is>
       </c>
       <c r="F201" s="3" t="inlineStr">
@@ -9035,12 +9036,12 @@
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>C29999</t>
+          <t>C29992</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29999</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29992</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
@@ -9050,7 +9051,7 @@
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>Lane stacking and the '+N more' overflow apply in day, week, and month views</t>
+          <t>Whole-order and multi-line shifts both read 'N Lines' on the block</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
@@ -9070,12 +9071,12 @@
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>C30001</t>
+          <t>C29995</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30001</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29995</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
@@ -9085,7 +9086,7 @@
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>Day view auto-scrolls to the working-day start; manual scrolling stands</t>
+          <t>The conflict icon is the only icon on a shift block</t>
         </is>
       </c>
       <c r="F203" s="3" t="inlineStr">
@@ -9105,12 +9106,12 @@
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>C30003</t>
+          <t>C29996</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30003</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29996</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
@@ -9120,7 +9121,7 @@
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>Date and time headers stick to the top during vertical scroll</t>
+          <t>Non-overlapping same-day shifts share one lane, even from different orders</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr">
@@ -9140,12 +9141,12 @@
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>C30005</t>
+          <t>C29997</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30005</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29997</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
@@ -9155,7 +9156,7 @@
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>Dragging a shift's left or right edge resizes its duration</t>
+          <t>Shifts whose times intersect split into stacked lanes and the row grows to fit</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
@@ -9175,12 +9176,12 @@
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>C30006</t>
+          <t>C29999</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30006</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29999</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
@@ -9190,7 +9191,7 @@
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>A now line marks the current time on today's day view, with a label on hover</t>
+          <t>Lane stacking and the '+N more' overflow apply in day, week, and month views</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
@@ -9210,12 +9211,12 @@
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>C30008</t>
+          <t>C30001</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30008</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30001</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
@@ -9225,7 +9226,7 @@
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>Clicking a shift opens its detail modal, with VIN always visible</t>
+          <t>Day view auto-scrolls to the working-day start; manual scrolling stands</t>
         </is>
       </c>
       <c r="F207" s="3" t="inlineStr">
@@ -9245,12 +9246,12 @@
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>C30009</t>
+          <t>C30003</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30009</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30003</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
@@ -9260,7 +9261,7 @@
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>Scheduled date and start/end time pickers work in 15-minute increments</t>
+          <t>Date and time headers stick to the top during vertical scroll</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr">
@@ -9280,12 +9281,12 @@
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>C30010</t>
+          <t>C30005</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30010</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30005</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
@@ -9295,7 +9296,7 @@
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>The modal shows the technician and time logged vs estimate progress</t>
+          <t>Dragging a shift's left or right edge resizes its duration</t>
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr">
@@ -9315,12 +9316,12 @@
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>C30011</t>
+          <t>C30006</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30011</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30006</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
@@ -9330,12 +9331,12 @@
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>The modal lists the scheduled line(s) with no money fields</t>
+          <t>A now line marks the current time on today's day view, with a label on hover</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
@@ -9350,12 +9351,12 @@
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>C30012</t>
+          <t>C30008</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30012</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30008</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
@@ -9365,12 +9366,12 @@
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>Estimated hours can be edited inline in the modal</t>
+          <t>Clicking a shift opens its detail modal, with VIN always visible</t>
         </is>
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
@@ -9385,12 +9386,12 @@
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>C30014</t>
+          <t>C30009</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30014</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30009</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
@@ -9400,7 +9401,7 @@
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>A conflicted shift's modal shows a conflict banner with an 'Adjust' action</t>
+          <t>Scheduled date and start/end time pickers work in 15-minute increments</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr">
@@ -9420,12 +9421,12 @@
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>C30016</t>
+          <t>C30010</t>
         </is>
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30016</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30010</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
@@ -9435,7 +9436,7 @@
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>Create an event via left-click 'Create Event' on empty grid space</t>
+          <t>The modal shows the technician and time logged vs estimate progress</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
@@ -9455,12 +9456,12 @@
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>C30017</t>
+          <t>C30011</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30017</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30011</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
@@ -9470,7 +9471,7 @@
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>Day view event creation shows a live preview block you can drag to resize</t>
+          <t>The modal lists the scheduled line(s) with no money fields</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
@@ -9490,12 +9491,12 @@
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>C30018</t>
+          <t>C30012</t>
         </is>
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30018</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30012</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
@@ -9505,7 +9506,7 @@
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>Event modal fields all save; the all-day toggle creates an all-day event</t>
+          <t>Estimated hours can be edited inline in the modal</t>
         </is>
       </c>
       <c r="F215" s="3" t="inlineStr">
@@ -9525,12 +9526,12 @@
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>C30021</t>
+          <t>C30014</t>
         </is>
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30021</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30014</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
@@ -9540,7 +9541,7 @@
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>Event cards look structurally distinct from shift cards</t>
+          <t>A conflicted shift's modal shows a conflict banner with an 'Adjust' action</t>
         </is>
       </c>
       <c r="F216" s="3" t="inlineStr">
@@ -9560,12 +9561,12 @@
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>C30022</t>
+          <t>C30016</t>
         </is>
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30022</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30016</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
@@ -9575,12 +9576,12 @@
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
-          <t>Events default to grey; choosing a color tints the card and chip</t>
+          <t>Create an event via left-click 'Create Event' on empty grid space</t>
         </is>
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
@@ -9595,12 +9596,12 @@
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>C30023</t>
+          <t>C30017</t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30023</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30017</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
@@ -9610,12 +9611,12 @@
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>Double-booked: two overlapping work orders on one technician are flagged</t>
+          <t>Day view event creation shows a live preview block you can drag to resize</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
@@ -9630,12 +9631,12 @@
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>C30024</t>
+          <t>C30018</t>
         </is>
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30024</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30018</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
@@ -9645,12 +9646,12 @@
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
-          <t>Working-day conflict: a shift outside the tech's working days is flagged</t>
+          <t>Event modal fields all save; the all-day toggle creates an all-day event</t>
         </is>
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
@@ -9665,12 +9666,12 @@
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>C30027</t>
+          <t>C30021</t>
         </is>
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30027</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30021</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
@@ -9680,7 +9681,7 @@
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
-          <t>The toolbar conflict pill shows the count and opens a list</t>
+          <t>Event cards look structurally distinct from shift cards</t>
         </is>
       </c>
       <c r="F220" s="3" t="inlineStr">
@@ -9700,12 +9701,12 @@
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>C30028</t>
+          <t>C30022</t>
         </is>
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30028</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30022</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
@@ -9715,7 +9716,7 @@
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
-          <t>Clicking a conflict in the dropdown navigates to the relevant technician and day</t>
+          <t>Events default to grey; choosing a color tints the card and chip</t>
         </is>
       </c>
       <c r="F221" s="3" t="inlineStr">
@@ -9735,12 +9736,12 @@
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>C30029</t>
+          <t>C30023</t>
         </is>
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30029</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30023</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
@@ -9750,7 +9751,7 @@
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>Red styling is only for conflicts and errors, never for overtime</t>
+          <t>Double-booked: two overlapping work orders on one technician are flagged</t>
         </is>
       </c>
       <c r="F222" s="3" t="inlineStr">
@@ -9770,12 +9771,12 @@
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>C30030</t>
+          <t>C30024</t>
         </is>
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30030</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30024</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
@@ -9785,7 +9786,7 @@
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
-          <t>Capacity bar fill = booked (shifts + events) vs available, clamped, equal tracks</t>
+          <t>Working-day conflict: a shift outside the tech's working days is flagged</t>
         </is>
       </c>
       <c r="F223" s="3" t="inlineStr">
@@ -9805,12 +9806,12 @@
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>C30031</t>
+          <t>C30027</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30031</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30027</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
@@ -9820,7 +9821,7 @@
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>Over capacity, an amber spill extends past the track's right edge</t>
+          <t>The toolbar conflict pill shows the count and opens a list</t>
         </is>
       </c>
       <c r="F224" s="3" t="inlineStr">
@@ -9840,12 +9841,12 @@
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>C30032</t>
+          <t>C30028</t>
         </is>
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30032</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30028</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
@@ -9855,7 +9856,7 @@
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>'OT' text tag appears when one technician exceeds their own daily hours</t>
+          <t>Clicking a conflict in the dropdown navigates to the relevant technician and day</t>
         </is>
       </c>
       <c r="F225" s="3" t="inlineStr">
@@ -9875,12 +9876,12 @@
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>C30033</t>
+          <t>C30029</t>
         </is>
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30033</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30029</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
@@ -9890,12 +9891,12 @@
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>Hovering a capacity bar shows a per-technician breakdown</t>
+          <t>Red styling is only for conflicts and errors, never for overtime</t>
         </is>
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
@@ -9910,12 +9911,12 @@
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>C30034</t>
+          <t>C30030</t>
         </is>
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30034</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30030</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
@@ -9925,7 +9926,7 @@
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>Shift hover tooltip shows the full shift summary incl. up to 3 line names</t>
+          <t>Capacity bar fill = booked (shifts + events) vs available, clamped, equal tracks</t>
         </is>
       </c>
       <c r="F227" s="3" t="inlineStr">
@@ -9945,12 +9946,12 @@
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>C30035</t>
+          <t>C30031</t>
         </is>
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30035</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30031</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
@@ -9960,7 +9961,7 @@
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>A conflicted shift's tooltip shows the icon and reason in amber</t>
+          <t>Over capacity, an amber spill extends past the track's right edge</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr">
@@ -9980,12 +9981,12 @@
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>C30036</t>
+          <t>C30032</t>
         </is>
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30036</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30032</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
@@ -9995,12 +9996,12 @@
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>Event hover tooltip shows name, grey category dot, time range and tech</t>
+          <t>'OT' text tag appears when one technician exceeds their own daily hours</t>
         </is>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
@@ -10015,12 +10016,12 @@
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>C30037</t>
+          <t>C30033</t>
         </is>
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30037</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30033</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr">
@@ -10030,7 +10031,7 @@
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>Tooltips open after a hover delay, dismiss on mouse-leave, are read-only</t>
+          <t>Hovering a capacity bar shows a per-technician breakdown</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr">
@@ -10050,12 +10051,12 @@
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>C30038</t>
+          <t>C30034</t>
         </is>
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30038</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30034</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr">
@@ -10065,7 +10066,7 @@
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>The tooltip flips or shifts to stay within the viewport - never clipped</t>
+          <t>Shift hover tooltip shows the full shift summary incl. up to 3 line names</t>
         </is>
       </c>
       <c r="F231" s="3" t="inlineStr">
@@ -10085,12 +10086,12 @@
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>C30039</t>
+          <t>C30035</t>
         </is>
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30039</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30035</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
@@ -10100,7 +10101,7 @@
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>'Today' button jumps the grid to the current date</t>
+          <t>A conflicted shift's tooltip shows the icon and reason in amber</t>
         </is>
       </c>
       <c r="F232" s="3" t="inlineStr">
@@ -10120,12 +10121,12 @@
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>C30040</t>
+          <t>C30036</t>
         </is>
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30040</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30036</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
@@ -10135,7 +10136,7 @@
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
-          <t>Left/right arrows step by day, week, or month to match the active range</t>
+          <t>Event hover tooltip shows name, grey category dot, time range and tech</t>
         </is>
       </c>
       <c r="F233" s="3" t="inlineStr">
@@ -10155,12 +10156,12 @@
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>C30052</t>
+          <t>C30037</t>
         </is>
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30052</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30037</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
@@ -10170,7 +10171,7 @@
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
-          <t>Dragging a shift to another technician row reassigns it, with a confirm modal</t>
+          <t>Tooltips open after a hover delay, dismiss on mouse-leave, are read-only</t>
         </is>
       </c>
       <c r="F234" s="3" t="inlineStr">
@@ -10190,12 +10191,12 @@
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>C30054</t>
+          <t>C30038</t>
         </is>
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30054</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30038</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
@@ -10205,7 +10206,7 @@
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
-          <t>Left-click empty grid space opens a menu: Create Event and New Work Order</t>
+          <t>The tooltip flips or shifts to stay within the viewport - never clipped</t>
         </is>
       </c>
       <c r="F235" s="3" t="inlineStr">
@@ -10225,12 +10226,12 @@
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>C30057</t>
+          <t>C30039</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30057</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30039</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
@@ -10240,12 +10241,12 @@
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
-          <t>Deleting a middle shift of a series offers all three scope options</t>
+          <t>'Today' button jumps the grid to the current date</t>
         </is>
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
@@ -10260,12 +10261,12 @@
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>C30058</t>
+          <t>C30040</t>
         </is>
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30058</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30040</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
@@ -10275,7 +10276,7 @@
       </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
-          <t>'This shift only' removes that day and the series keeps the gap</t>
+          <t>Left/right arrows step by day, week, or month to match the active range</t>
         </is>
       </c>
       <c r="F237" s="3" t="inlineStr">
@@ -10295,12 +10296,12 @@
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>C30059</t>
+          <t>C30052</t>
         </is>
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30059</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30052</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
@@ -10310,7 +10311,7 @@
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>'This and everything after' removes from the clicked shift onward</t>
+          <t>Dragging a shift to another technician row reassigns it, with a confirm modal</t>
         </is>
       </c>
       <c r="F238" s="3" t="inlineStr">
@@ -10330,12 +10331,12 @@
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>C30060</t>
+          <t>C30054</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30060</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30054</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
@@ -10345,12 +10346,12 @@
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
-          <t>'The whole series' removes all of the series' shifts for that technician</t>
+          <t>Left-click empty grid space opens a menu: Create Event and New Work Order</t>
         </is>
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -10365,12 +10366,12 @@
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>C30061</t>
+          <t>C30057</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30061</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30057</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
@@ -10380,12 +10381,12 @@
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
-          <t>Scope options adapt: the first and last shift each show only two</t>
+          <t>Deleting a middle shift of a series offers all three scope options</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
@@ -10400,12 +10401,12 @@
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>C30062</t>
+          <t>C30058</t>
         </is>
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30062</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30058</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
@@ -10415,7 +10416,7 @@
       </c>
       <c r="E241" s="3" t="inlineStr">
         <is>
-          <t>Deleting a standalone (non-series) shift does not ask for a series scope</t>
+          <t>'This shift only' removes that day and the series keeps the gap</t>
         </is>
       </c>
       <c r="F241" s="3" t="inlineStr">
@@ -10435,12 +10436,12 @@
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>C30064</t>
+          <t>C30059</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30064</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30059</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
@@ -10450,7 +10451,7 @@
       </c>
       <c r="E242" s="3" t="inlineStr">
         <is>
-          <t>Toast lasts ~7s with Undo (about 4s without); stays on hover, goes on leave</t>
+          <t>'This and everything after' removes from the clicked shift onward</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr">
@@ -10470,12 +10471,12 @@
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>C30065</t>
+          <t>C30060</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30065</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30060</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
@@ -10485,7 +10486,7 @@
       </c>
       <c r="E243" s="3" t="inlineStr">
         <is>
-          <t>Every create/delete/move/reassign toasts with Undo, and Undo restores</t>
+          <t>'The whole series' removes all of the series' shifts for that technician</t>
         </is>
       </c>
       <c r="F243" s="3" t="inlineStr">
@@ -10505,12 +10506,12 @@
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>C30066</t>
+          <t>C30061</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30066</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30061</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
@@ -10520,7 +10521,7 @@
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
-          <t>Escape closes the topmost open modal or popover, following the stacking order</t>
+          <t>Scope options adapt: the first and last shift each show only two</t>
         </is>
       </c>
       <c r="F244" s="3" t="inlineStr">
@@ -10540,12 +10541,12 @@
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>C30068</t>
+          <t>C30062</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30068</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30062</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
@@ -10555,7 +10556,7 @@
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
-          <t>Enter confirms the active dialog, but not inside a note textarea</t>
+          <t>Deleting a standalone (non-series) shift does not ask for a series scope</t>
         </is>
       </c>
       <c r="F245" s="3" t="inlineStr">
@@ -10575,12 +10576,12 @@
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>C30070</t>
+          <t>C30064</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30070</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30064</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
@@ -10590,7 +10591,7 @@
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>Modals trap focus and all interactive elements are keyboard-reachable</t>
+          <t>Toast lasts ~7s with Undo (about 4s without); stays on hover, goes on leave</t>
         </is>
       </c>
       <c r="F246" s="3" t="inlineStr">
@@ -10610,12 +10611,12 @@
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>C30071</t>
+          <t>C30065</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30071</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30065</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
@@ -10625,7 +10626,7 @@
       </c>
       <c r="E247" s="3" t="inlineStr">
         <is>
-          <t>Blue is the default color for all shifts, including long and multi-week jobs</t>
+          <t>Every create/delete/move/reassign toasts with Undo, and Undo restores</t>
         </is>
       </c>
       <c r="F247" s="3" t="inlineStr">
@@ -10645,12 +10646,12 @@
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>C30072</t>
+          <t>C30066</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30072</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30066</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
@@ -10660,7 +10661,7 @@
       </c>
       <c r="E248" s="3" t="inlineStr">
         <is>
-          <t>Shift modal color picker recolors that shift only, in matching tones</t>
+          <t>Escape closes the topmost open modal or popover, following the stacking order</t>
         </is>
       </c>
       <c r="F248" s="3" t="inlineStr">
@@ -10680,12 +10681,12 @@
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>C30073</t>
+          <t>C30068</t>
         </is>
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30073</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30068</t>
         </is>
       </c>
       <c r="D249" s="3" t="inlineStr">
@@ -10695,7 +10696,7 @@
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
-          <t>Color labels are editable per shop</t>
+          <t>Enter confirms the active dialog, but not inside a note textarea</t>
         </is>
       </c>
       <c r="F249" s="3" t="inlineStr">
@@ -10715,12 +10716,12 @@
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>C30074</t>
+          <t>C30070</t>
         </is>
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30074</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30070</t>
         </is>
       </c>
       <c r="D250" s="3" t="inlineStr">
@@ -10730,7 +10731,7 @@
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
-          <t>Schedule: View grants the full read-only experience across the whole page</t>
+          <t>Modals trap focus and all interactive elements are keyboard-reachable</t>
         </is>
       </c>
       <c r="F250" s="3" t="inlineStr">
@@ -10750,12 +10751,12 @@
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>C30075</t>
+          <t>C30071</t>
         </is>
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30075</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30071</t>
         </is>
       </c>
       <c r="D251" s="3" t="inlineStr">
@@ -10765,7 +10766,7 @@
       </c>
       <c r="E251" s="3" t="inlineStr">
         <is>
-          <t>View-only: every editing affordance is hidden or disabled</t>
+          <t>Blue is the default color for all shifts, including long and multi-week jobs</t>
         </is>
       </c>
       <c r="F251" s="3" t="inlineStr">
@@ -10785,12 +10786,12 @@
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>C30076</t>
+          <t>C30072</t>
         </is>
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30076</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30072</t>
         </is>
       </c>
       <c r="D252" s="3" t="inlineStr">
@@ -10800,7 +10801,7 @@
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
-          <t>With Schedule: View OFF, the Schedule top-level nav item is hidden entirely</t>
+          <t>Shift modal color picker recolors that shift only, in matching tones</t>
         </is>
       </c>
       <c r="F252" s="3" t="inlineStr">
@@ -10820,12 +10821,12 @@
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>C30077</t>
+          <t>C30073</t>
         </is>
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30077</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30073</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
@@ -10835,7 +10836,7 @@
       </c>
       <c r="E253" s="3" t="inlineStr">
         <is>
-          <t>Schedule: Edit unlocks all creation and modification interactions</t>
+          <t>Color labels are editable per shop</t>
         </is>
       </c>
       <c r="F253" s="3" t="inlineStr">
@@ -10855,12 +10856,12 @@
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>C30078</t>
+          <t>C30076</t>
         </is>
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30078</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30076</t>
         </is>
       </c>
       <c r="D254" s="3" t="inlineStr">
@@ -10870,7 +10871,7 @@
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
-          <t>Edit without Delete: the user can create and modify but not remove</t>
+          <t>With Schedule: View OFF, the Schedule top-level nav item is hidden entirely</t>
         </is>
       </c>
       <c r="F254" s="3" t="inlineStr">
@@ -10890,12 +10891,12 @@
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>C30079</t>
+          <t>C30077</t>
         </is>
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30079</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30077</t>
         </is>
       </c>
       <c r="D255" s="3" t="inlineStr">
@@ -10905,12 +10906,12 @@
       </c>
       <c r="E255" s="3" t="inlineStr">
         <is>
-          <t>Schedule: Delete unlocks deleting shifts and events</t>
+          <t>Schedule: Edit unlocks all creation and modification interactions</t>
         </is>
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
@@ -10925,12 +10926,12 @@
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>C30080</t>
+          <t>C30078</t>
         </is>
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30080</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30078</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
@@ -10940,7 +10941,7 @@
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
-          <t>Permission tiers nest: Delete requires Edit, Edit requires View</t>
+          <t>Edit without Delete: the user can create and modify but not remove</t>
         </is>
       </c>
       <c r="F256" s="3" t="inlineStr">
@@ -10960,12 +10961,12 @@
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>C30081</t>
+          <t>C30079</t>
         </is>
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30081</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30079</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
@@ -10975,7 +10976,7 @@
       </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
-          <t>Schedule without Work Orders: View - the sidebar hides the work order list</t>
+          <t>Schedule: Delete unlocks deleting shifts and events</t>
         </is>
       </c>
       <c r="F257" s="3" t="inlineStr">
@@ -10995,12 +10996,12 @@
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>C30083</t>
+          <t>C30080</t>
         </is>
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30083</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30080</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
@@ -11010,7 +11011,7 @@
       </c>
       <c r="E258" s="3" t="inlineStr">
         <is>
-          <t>Grid rows are department-based, not role-based</t>
+          <t>Permission tiers nest: Delete requires Edit, Edit requires View</t>
         </is>
       </c>
       <c r="F258" s="3" t="inlineStr">
@@ -11030,12 +11031,12 @@
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>C30084</t>
+          <t>C30081</t>
         </is>
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30084</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30081</t>
         </is>
       </c>
       <c r="D259" s="3" t="inlineStr">
@@ -11045,12 +11046,12 @@
       </c>
       <c r="E259" s="3" t="inlineStr">
         <is>
-          <t>Clocking into line tasks is gated by the staff 'Time Clock' setting</t>
+          <t>Schedule without Work Orders: View - the sidebar hides the work order list</t>
         </is>
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>Part of the 12 August build check: the build stamp at the bottom of the case was re-cut to the build running today. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
@@ -11065,12 +11066,12 @@
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>C30086</t>
+          <t>C30083</t>
         </is>
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30086</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30083</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
@@ -11080,7 +11081,7 @@
       </c>
       <c r="E260" s="3" t="inlineStr">
         <is>
-          <t>Below 960px the grid scrolls sideways and the sidebar collapses</t>
+          <t>Grid rows are department-based, not role-based</t>
         </is>
       </c>
       <c r="F260" s="3" t="inlineStr">
@@ -11100,12 +11101,12 @@
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>C30087</t>
+          <t>C30084</t>
         </is>
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30087</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30084</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
@@ -11115,12 +11116,12 @@
       </c>
       <c r="E261" s="3" t="inlineStr">
         <is>
-          <t>The sidebar work order list and line drill-down stay smooth with 50+ items</t>
+          <t>Clocking into line tasks is gated by the staff 'Time Clock' setting</t>
         </is>
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>Part of the 12 August build check: the build stamp at the bottom of the case was re-cut to the build running today. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
@@ -11135,12 +11136,12 @@
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>C30088</t>
+          <t>C30086</t>
         </is>
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30088</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30086</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
@@ -11150,7 +11151,7 @@
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
-          <t>The grid renders smoothly at full load - 15 technicians over 7 days</t>
+          <t>Below 960px the grid scrolls sideways and the sidebar collapses</t>
         </is>
       </c>
       <c r="F262" s="3" t="inlineStr">
@@ -11170,12 +11171,12 @@
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>C30089</t>
+          <t>C30087</t>
         </is>
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30089</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30087</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
@@ -11185,7 +11186,7 @@
       </c>
       <c r="E263" s="3" t="inlineStr">
         <is>
-          <t>Shop closures do NOT block spread in V1 - shifts can land on closure days</t>
+          <t>The sidebar work order list and line drill-down stay smooth with 50+ items</t>
         </is>
       </c>
       <c r="F263" s="3" t="inlineStr">
@@ -11205,12 +11206,12 @@
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>C30090</t>
+          <t>C30088</t>
         </is>
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30090</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30088</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
@@ -11220,7 +11221,7 @@
       </c>
       <c r="E264" s="3" t="inlineStr">
         <is>
-          <t>Scheduled, estimated and actual clocked hours are three separate numbers</t>
+          <t>The grid renders smoothly at full load - 15 technicians over 7 days</t>
         </is>
       </c>
       <c r="F264" s="3" t="inlineStr">
@@ -11240,12 +11241,12 @@
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>C30614</t>
+          <t>C30089</t>
         </is>
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30614</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30089</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
@@ -11255,7 +11256,7 @@
       </c>
       <c r="E265" s="3" t="inlineStr">
         <is>
-          <t>With Work Orders: View OFF, work order details on shifts are hidden</t>
+          <t>Shop closures do NOT block spread in V1 - shifts can land on closure days</t>
         </is>
       </c>
       <c r="F265" s="3" t="inlineStr">
@@ -11275,12 +11276,12 @@
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>C30615</t>
+          <t>C30090</t>
         </is>
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30615</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30090</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
@@ -11290,7 +11291,7 @@
       </c>
       <c r="E266" s="3" t="inlineStr">
         <is>
-          <t>An event's hours count toward the capacity bar but raise no conflict</t>
+          <t>Scheduled, estimated and actual clocked hours are three separate numbers</t>
         </is>
       </c>
       <c r="F266" s="3" t="inlineStr">
@@ -11310,12 +11311,12 @@
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>C38851</t>
+          <t>C30614</t>
         </is>
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/38851</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30614</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
@@ -11325,7 +11326,7 @@
       </c>
       <c r="E267" s="3" t="inlineStr">
         <is>
-          <t>Overlapping hour ranges block Save; incomplete rows are ignored</t>
+          <t>With Work Orders: View OFF, work order details on shifts are hidden</t>
         </is>
       </c>
       <c r="F267" s="3" t="inlineStr">
@@ -11345,12 +11346,12 @@
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>C38855</t>
+          <t>C30615</t>
         </is>
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/38855</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30615</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
@@ -11360,7 +11361,7 @@
       </c>
       <c r="E268" s="3" t="inlineStr">
         <is>
-          <t>'New Work Order' in the cell menu points the user to the Work Orders tab</t>
+          <t>An event's hours count toward the capacity bar but raise no conflict</t>
         </is>
       </c>
       <c r="F268" s="3" t="inlineStr">
@@ -11380,12 +11381,12 @@
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>C38863</t>
+          <t>C38851</t>
         </is>
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/38863</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/38851</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
@@ -11395,7 +11396,7 @@
       </c>
       <c r="E269" s="3" t="inlineStr">
         <is>
-          <t>Spread past 8 weeks asks to confirm; a series can never exceed 120 shifts</t>
+          <t>Overlapping hour ranges block Save; incomplete rows are ignored</t>
         </is>
       </c>
       <c r="F269" s="3" t="inlineStr">
@@ -11415,12 +11416,12 @@
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>C38864</t>
+          <t>C38855</t>
         </is>
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/38864</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/38855</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
@@ -11430,12 +11431,12 @@
       </c>
       <c r="E270" s="3" t="inlineStr">
         <is>
-          <t>Schedule actions save immediately - Undo reverses them, closing does not cancel</t>
+          <t>'New Work Order' in the cell menu points the user to the Work Orders tab</t>
         </is>
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Edited in the verify-final-2026-08-12 pass. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
@@ -11450,12 +11451,12 @@
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>C38865</t>
+          <t>C38863</t>
         </is>
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/38865</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/38863</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
@@ -11465,7 +11466,7 @@
       </c>
       <c r="E271" s="3" t="inlineStr">
         <is>
-          <t>A multi-week series keeps the same local start time across the clock change</t>
+          <t>Spread past 8 weeks asks to confirm; a series can never exceed 120 shifts</t>
         </is>
       </c>
       <c r="F271" s="3" t="inlineStr">
@@ -11485,12 +11486,12 @@
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>C38866</t>
+          <t>C38864</t>
         </is>
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/38866</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/38864</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
@@ -11500,12 +11501,12 @@
       </c>
       <c r="E272" s="3" t="inlineStr">
         <is>
-          <t>Schedule and all its dialogs display correctly in dark mode</t>
+          <t>Schedule actions save immediately - Undo reverses them, closing does not cancel</t>
         </is>
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
-          <t>Correction from the 11 August build check. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
@@ -11520,12 +11521,12 @@
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>C38867</t>
+          <t>C38865</t>
         </is>
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/38867</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/38865</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
@@ -11535,7 +11536,7 @@
       </c>
       <c r="E273" s="3" t="inlineStr">
         <is>
-          <t>Shifts and events created before the Schedule rewrite still appear after it</t>
+          <t>A multi-week series keeps the same local start time across the clock change</t>
         </is>
       </c>
       <c r="F273" s="3" t="inlineStr">
@@ -11555,12 +11556,12 @@
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>C38868</t>
+          <t>C38866</t>
         </is>
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/38868</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/38866</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
@@ -11570,12 +11571,12 @@
       </c>
       <c r="E274" s="3" t="inlineStr">
         <is>
-          <t>Dashboard shows one schedule row per work order even with many shifts</t>
+          <t>Schedule and all its dialogs display correctly in dark mode</t>
         </is>
       </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
-          <t>The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
+          <t>Correction from the 11 August build check. The date we read each source ('read on 11 August 2026') was added to the sourcing line at the bottom of the expected results. Nothing a tester reads, and nothing a check evaluates, changed.</t>
         </is>
       </c>
       <c r="G274" s="3" t="inlineStr">
@@ -11590,12 +11591,12 @@
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>C38869</t>
+          <t>C38867</t>
         </is>
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/38869</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/38867</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
@@ -11605,7 +11606,7 @@
       </c>
       <c r="E275" s="3" t="inlineStr">
         <is>
-          <t>A work order created with an appointment shows up on the Schedule board</t>
+          <t>Shifts and events created before the Schedule rewrite still appear after it</t>
         </is>
       </c>
       <c r="F275" s="3" t="inlineStr">
@@ -11625,12 +11626,12 @@
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>C38870</t>
+          <t>C38868</t>
         </is>
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/38870</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/38868</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
@@ -11640,7 +11641,7 @@
       </c>
       <c r="E276" s="3" t="inlineStr">
         <is>
-          <t>A multi-location technician's shift appears only on the work order's location</t>
+          <t>Dashboard shows one schedule row per work order even with many shifts</t>
         </is>
       </c>
       <c r="F276" s="3" t="inlineStr">
@@ -11660,12 +11661,12 @@
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>C38871</t>
+          <t>C38869</t>
         </is>
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/38871</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/38869</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr">
@@ -11675,7 +11676,7 @@
       </c>
       <c r="E277" s="3" t="inlineStr">
         <is>
-          <t>Work order form offers a Priority (High/Medium/Low) that drives the sidebar</t>
+          <t>A work order created with an appointment shows up on the Schedule board</t>
         </is>
       </c>
       <c r="F277" s="3" t="inlineStr">
@@ -11695,12 +11696,12 @@
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>C38872</t>
+          <t>C38870</t>
         </is>
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/38872</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/38870</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
@@ -11710,7 +11711,7 @@
       </c>
       <c r="E278" s="3" t="inlineStr">
         <is>
-          <t>API - Schedule reads need View; writes need Edit; deletes need Delete (403)</t>
+          <t>A multi-location technician's shift appears only on the work order's location</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr">
@@ -11730,12 +11731,12 @@
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>C38873</t>
+          <t>C38871</t>
         </is>
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/38873</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/38871</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
@@ -11745,7 +11746,7 @@
       </c>
       <c r="E279" s="3" t="inlineStr">
         <is>
-          <t>API - Series past 8 weeks returns 409 until acknowledged; over 120 shifts 422</t>
+          <t>Work order form offers a Priority (High/Medium/Low) that drives the sidebar</t>
         </is>
       </c>
       <c r="F279" s="3" t="inlineStr">
@@ -11765,12 +11766,12 @@
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>C38874</t>
+          <t>C38873</t>
         </is>
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/38874</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/38873</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
@@ -11780,7 +11781,7 @@
       </c>
       <c r="E280" s="3" t="inlineStr">
         <is>
-          <t>API - No pricing fields in Schedule responses; WO details need Work Orders View</t>
+          <t>API - Series past 8 weeks returns 409 until acknowledged; over 120 shifts 422</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr">
